--- a/data_management2026/database.xlsx
+++ b/data_management2026/database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\學校\清大\LAB\AHG\kit\github\RealTimeAccompaniment_COPY\data_management2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/estherchen/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39FA73A3-AFCA-4420-B91D-4966DD4CC3D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D4D49D-4F30-E343-88E8-E4A2A180AD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="435" windowWidth="15930" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29080" windowHeight="16540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2697" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2713" uniqueCount="712">
   <si>
     <t>entry</t>
   </si>
@@ -2148,6 +2148,54 @@
   </si>
   <si>
     <t>陳禹之or曲友友</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\Heidenroslein\Heidenroslein_accomp\inputinterpretation.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heidenroslein\Heidenroslein_accomp\inputmsglog.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heidenroslein\Heidenroslein_accomp\outputscore.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heidenroslein_accomp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>unknown AI</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>unknown</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\Heidenroslein\Heidenroslein_melody\inputinterpretation.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heidenroslein\Heidenroslein_melody\inputmsglog.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heidenroslein_melody</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heidenroslein\Heidenroslein_melody\outputscore.txt</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_management2026\py_scripts_and_notes\extract_interpretation_Heidenroslein.py</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2155,7 +2203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2558,22 +2606,22 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K323"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K325"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.59765625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="38" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="36.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.59765625" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="20.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2608,7 +2656,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="18.75" customHeight="1">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -2640,7 +2688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="18.75" customHeight="1">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -2672,7 +2720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="18.75" customHeight="1">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -2704,7 +2752,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18.75" customHeight="1">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -2736,7 +2784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="18.75" customHeight="1">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -2768,7 +2816,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18.75" customHeight="1">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -2800,7 +2848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="18.75" customHeight="1">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -2832,7 +2880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="18.75" customHeight="1">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -2864,7 +2912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="18.75" customHeight="1">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -2896,7 +2944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="18.75" customHeight="1">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -2928,7 +2976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="18.75" customHeight="1">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -2960,7 +3008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="18.75" customHeight="1">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -2992,7 +3040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="18.75" customHeight="1">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -3024,7 +3072,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="18.75" customHeight="1">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -3056,7 +3104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="18.75" customHeight="1">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -3088,7 +3136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="18.75" customHeight="1">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -3120,7 +3168,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="18.75" customHeight="1">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -3152,7 +3200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="18.75" customHeight="1">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -3184,7 +3232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="18.75" customHeight="1">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -3216,7 +3264,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="18.75" customHeight="1">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -3248,7 +3296,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="18.75" customHeight="1">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -3280,7 +3328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="18.75" customHeight="1">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -3312,7 +3360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="18.75" customHeight="1">
       <c r="A24" s="3">
         <v>23</v>
       </c>
@@ -3344,7 +3392,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="18.75" customHeight="1">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -3376,7 +3424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="18.75" customHeight="1">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -3408,7 +3456,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="18.75" customHeight="1">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -3440,7 +3488,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="18.75" customHeight="1">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -3472,7 +3520,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="18.75" customHeight="1">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -3504,7 +3552,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="18.75" customHeight="1">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -3536,7 +3584,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="18.75" customHeight="1">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -3568,7 +3616,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="18.75" customHeight="1">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -3600,7 +3648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" ht="18.75" customHeight="1">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -3632,7 +3680,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" ht="18.75" customHeight="1">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -3664,7 +3712,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="18.75" customHeight="1">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -3696,7 +3744,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" ht="18.75" customHeight="1">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -3728,7 +3776,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" ht="18.75" customHeight="1">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -3760,7 +3808,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" ht="18.75" customHeight="1">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -3792,7 +3840,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="18.75" customHeight="1">
       <c r="A39" s="3">
         <v>38</v>
       </c>
@@ -3824,7 +3872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="18.75" customHeight="1">
       <c r="A40" s="3">
         <v>39</v>
       </c>
@@ -3856,7 +3904,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" ht="18.75" customHeight="1">
       <c r="A41" s="3">
         <v>40</v>
       </c>
@@ -3888,7 +3936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" ht="18.75" customHeight="1">
       <c r="A42" s="3">
         <v>41</v>
       </c>
@@ -3920,7 +3968,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="18.75" customHeight="1">
       <c r="A43" s="3">
         <v>42</v>
       </c>
@@ -3952,7 +4000,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="18.75" customHeight="1">
       <c r="A44" s="3">
         <v>43</v>
       </c>
@@ -3984,7 +4032,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" ht="18.75" customHeight="1">
       <c r="A45" s="3">
         <v>44</v>
       </c>
@@ -4016,7 +4064,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="18.75" customHeight="1">
       <c r="A46" s="3">
         <v>45</v>
       </c>
@@ -4048,7 +4096,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" ht="18.75" customHeight="1">
       <c r="A47" s="3">
         <v>46</v>
       </c>
@@ -4080,7 +4128,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" ht="18.75" customHeight="1">
       <c r="A48" s="3">
         <v>47</v>
       </c>
@@ -4112,7 +4160,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="18.75" customHeight="1">
       <c r="A49" s="3">
         <v>48</v>
       </c>
@@ -4144,7 +4192,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="18.75" customHeight="1">
       <c r="A50" s="3">
         <v>49</v>
       </c>
@@ -4176,7 +4224,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="18.75" customHeight="1">
       <c r="A51" s="3">
         <v>50</v>
       </c>
@@ -4208,7 +4256,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="18.75" customHeight="1">
       <c r="A52" s="3">
         <v>51</v>
       </c>
@@ -4240,7 +4288,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="18.75" customHeight="1">
       <c r="A53" s="3">
         <v>52</v>
       </c>
@@ -4272,7 +4320,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="18.75" customHeight="1">
       <c r="A54" s="3">
         <v>53</v>
       </c>
@@ -4304,7 +4352,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" ht="18.75" customHeight="1">
       <c r="A55" s="3">
         <v>54</v>
       </c>
@@ -4336,7 +4384,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" ht="18.75" customHeight="1">
       <c r="A56" s="3">
         <v>55</v>
       </c>
@@ -4368,7 +4416,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" ht="18.75" customHeight="1">
       <c r="A57" s="3">
         <v>56</v>
       </c>
@@ -4400,7 +4448,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" ht="18.75" customHeight="1">
       <c r="A58" s="3">
         <v>57</v>
       </c>
@@ -4432,7 +4480,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" ht="18.75" customHeight="1">
       <c r="A59" s="3">
         <v>58</v>
       </c>
@@ -4464,7 +4512,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" ht="18.75" customHeight="1">
       <c r="A60" s="3">
         <v>59</v>
       </c>
@@ -4496,7 +4544,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" ht="18.75" customHeight="1">
       <c r="A61" s="3">
         <v>60</v>
       </c>
@@ -4528,7 +4576,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" ht="18.75" customHeight="1">
       <c r="A62" s="3">
         <v>61</v>
       </c>
@@ -4560,7 +4608,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" ht="18.75" customHeight="1">
       <c r="A63" s="3">
         <v>62</v>
       </c>
@@ -4592,7 +4640,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" ht="18.75" customHeight="1">
       <c r="A64" s="3">
         <v>63</v>
       </c>
@@ -4624,7 +4672,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" ht="18.75" customHeight="1">
       <c r="A65" s="3">
         <v>64</v>
       </c>
@@ -4656,7 +4704,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" ht="18.75" customHeight="1">
       <c r="A66" s="3">
         <v>65</v>
       </c>
@@ -4688,7 +4736,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" ht="18.75" customHeight="1">
       <c r="A67" s="3">
         <v>66</v>
       </c>
@@ -4720,7 +4768,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" ht="18.75" customHeight="1">
       <c r="A68" s="3">
         <v>67</v>
       </c>
@@ -4752,7 +4800,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" ht="18.75" customHeight="1">
       <c r="A69" s="3">
         <v>68</v>
       </c>
@@ -4784,7 +4832,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="18.75" customHeight="1">
       <c r="A70" s="3">
         <v>69</v>
       </c>
@@ -4816,7 +4864,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="18.75" customHeight="1">
       <c r="A71" s="3">
         <v>70</v>
       </c>
@@ -4848,7 +4896,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" ht="18.75" customHeight="1">
       <c r="A72" s="3">
         <v>71</v>
       </c>
@@ -4880,7 +4928,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="18.75" customHeight="1">
       <c r="A73" s="3">
         <v>72</v>
       </c>
@@ -4912,7 +4960,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" ht="18.75" customHeight="1">
       <c r="A74" s="3">
         <v>73</v>
       </c>
@@ -4944,7 +4992,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" ht="18.75" customHeight="1">
       <c r="A75" s="3">
         <v>74</v>
       </c>
@@ -4976,7 +5024,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" ht="18.75" customHeight="1">
       <c r="A76" s="3">
         <v>75</v>
       </c>
@@ -5008,7 +5056,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" ht="18.75" customHeight="1">
       <c r="A77" s="3">
         <v>76</v>
       </c>
@@ -5040,7 +5088,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="18.75" customHeight="1">
       <c r="A78" s="3">
         <v>77</v>
       </c>
@@ -5072,7 +5120,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" ht="18.75" customHeight="1">
       <c r="A79" s="3">
         <v>78</v>
       </c>
@@ -5104,7 +5152,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" ht="18.75" customHeight="1">
       <c r="A80" s="3">
         <v>79</v>
       </c>
@@ -5136,7 +5184,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" ht="18.75" customHeight="1">
       <c r="A81" s="3">
         <v>80</v>
       </c>
@@ -5168,7 +5216,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="18.75" customHeight="1">
       <c r="A82" s="3">
         <v>81</v>
       </c>
@@ -5200,7 +5248,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" ht="18.75" customHeight="1">
       <c r="A83" s="3">
         <v>82</v>
       </c>
@@ -5232,7 +5280,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" ht="18.75" customHeight="1">
       <c r="A84" s="3">
         <v>83</v>
       </c>
@@ -5264,7 +5312,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" ht="18.75" customHeight="1">
       <c r="A85" s="3">
         <v>84</v>
       </c>
@@ -5296,7 +5344,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="18.75" customHeight="1">
       <c r="A86" s="3">
         <v>85</v>
       </c>
@@ -5328,7 +5376,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="18.75" customHeight="1">
       <c r="A87" s="3">
         <v>86</v>
       </c>
@@ -5360,7 +5408,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" ht="18.75" customHeight="1">
       <c r="A88" s="3">
         <v>87</v>
       </c>
@@ -5392,7 +5440,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" ht="18.75" customHeight="1">
       <c r="A89" s="3">
         <v>88</v>
       </c>
@@ -5424,7 +5472,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" ht="18.75" customHeight="1">
       <c r="A90" s="3">
         <v>89</v>
       </c>
@@ -5456,7 +5504,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" ht="18.75" customHeight="1">
       <c r="A91" s="3">
         <v>90</v>
       </c>
@@ -5488,7 +5536,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" ht="18.75" customHeight="1">
       <c r="A92" s="3">
         <v>91</v>
       </c>
@@ -5520,7 +5568,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" ht="18.75" customHeight="1">
       <c r="A93" s="3">
         <v>92</v>
       </c>
@@ -5552,7 +5600,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" ht="18.75" customHeight="1">
       <c r="A94" s="3">
         <v>93</v>
       </c>
@@ -5584,7 +5632,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" ht="18.75" customHeight="1">
       <c r="A95" s="3">
         <v>94</v>
       </c>
@@ -5616,7 +5664,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="18.75" customHeight="1">
       <c r="A96" s="3">
         <v>95</v>
       </c>
@@ -5648,7 +5696,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" ht="18.75" customHeight="1">
       <c r="A97" s="3">
         <v>96</v>
       </c>
@@ -5680,7 +5728,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" ht="18.75" customHeight="1">
       <c r="A98" s="3">
         <v>97</v>
       </c>
@@ -5712,7 +5760,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" ht="18.75" customHeight="1">
       <c r="A99" s="3">
         <v>98</v>
       </c>
@@ -5744,7 +5792,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" ht="18.75" customHeight="1">
       <c r="A100" s="3">
         <v>99</v>
       </c>
@@ -5776,7 +5824,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" ht="18.75" customHeight="1">
       <c r="A101" s="3">
         <v>100</v>
       </c>
@@ -5808,7 +5856,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" ht="18.75" customHeight="1">
       <c r="A102" s="3">
         <v>101</v>
       </c>
@@ -5840,7 +5888,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" ht="18.75" customHeight="1">
       <c r="A103" s="3">
         <v>102</v>
       </c>
@@ -5872,7 +5920,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" ht="18.75" customHeight="1">
       <c r="A104" s="3">
         <v>103</v>
       </c>
@@ -5904,7 +5952,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" ht="18.75" customHeight="1">
       <c r="A105" s="3">
         <v>104</v>
       </c>
@@ -5936,7 +5984,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" ht="18.75" customHeight="1">
       <c r="A106" s="3">
         <v>105</v>
       </c>
@@ -5968,7 +6016,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" ht="18.75" customHeight="1">
       <c r="A107" s="3">
         <v>106</v>
       </c>
@@ -6000,7 +6048,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="18.75" customHeight="1">
       <c r="A108" s="3">
         <v>107</v>
       </c>
@@ -6032,7 +6080,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" ht="18.75" customHeight="1">
       <c r="A109" s="3">
         <v>108</v>
       </c>
@@ -6064,7 +6112,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" ht="18.75" customHeight="1">
       <c r="A110" s="3">
         <v>109</v>
       </c>
@@ -6096,7 +6144,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" ht="18.75" customHeight="1">
       <c r="A111" s="3">
         <v>110</v>
       </c>
@@ -6128,7 +6176,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" ht="18.75" customHeight="1">
       <c r="A112" s="3">
         <v>111</v>
       </c>
@@ -6160,7 +6208,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="18.75" customHeight="1">
       <c r="A113" s="3">
         <v>112</v>
       </c>
@@ -6192,7 +6240,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" ht="18.75" customHeight="1">
       <c r="A114" s="3">
         <v>113</v>
       </c>
@@ -6224,7 +6272,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" ht="18.75" customHeight="1">
       <c r="A115" s="3">
         <v>114</v>
       </c>
@@ -6256,7 +6304,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="18.75" customHeight="1">
       <c r="A116" s="3">
         <v>115</v>
       </c>
@@ -6288,7 +6336,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" ht="18.75" customHeight="1">
       <c r="A117" s="3">
         <v>116</v>
       </c>
@@ -6320,7 +6368,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" ht="18.75" customHeight="1">
       <c r="A118" s="3">
         <v>117</v>
       </c>
@@ -6352,7 +6400,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" ht="18.75" customHeight="1">
       <c r="A119" s="3">
         <v>118</v>
       </c>
@@ -6384,7 +6432,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" ht="18.75" customHeight="1">
       <c r="A120" s="3">
         <v>119</v>
       </c>
@@ -6416,7 +6464,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="18.75" customHeight="1">
       <c r="A121" s="3">
         <v>120</v>
       </c>
@@ -6448,7 +6496,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" ht="18.75" customHeight="1">
       <c r="A122" s="3">
         <v>121</v>
       </c>
@@ -6480,7 +6528,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="18.75" customHeight="1">
       <c r="A123" s="3">
         <v>122</v>
       </c>
@@ -6512,7 +6560,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" ht="18.75" customHeight="1">
       <c r="A124" s="3">
         <v>123</v>
       </c>
@@ -6544,7 +6592,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" ht="18.75" customHeight="1">
       <c r="A125" s="3">
         <v>124</v>
       </c>
@@ -6576,7 +6624,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" ht="18.75" customHeight="1">
       <c r="A126" s="3">
         <v>125</v>
       </c>
@@ -6608,7 +6656,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" ht="18.75" customHeight="1">
       <c r="A127" s="3">
         <v>126</v>
       </c>
@@ -6640,7 +6688,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" ht="18.75" customHeight="1">
       <c r="A128" s="3">
         <v>127</v>
       </c>
@@ -6672,7 +6720,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" ht="18.75" customHeight="1">
       <c r="A129" s="3">
         <v>128</v>
       </c>
@@ -6704,7 +6752,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" ht="18.75" customHeight="1">
       <c r="A130" s="3">
         <v>129</v>
       </c>
@@ -6736,7 +6784,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" ht="18.75" customHeight="1">
       <c r="A131" s="3">
         <v>130</v>
       </c>
@@ -6768,7 +6816,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" ht="18.75" customHeight="1">
       <c r="A132" s="3">
         <v>131</v>
       </c>
@@ -6800,7 +6848,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" ht="18.75" customHeight="1">
       <c r="A133" s="3">
         <v>132</v>
       </c>
@@ -6832,7 +6880,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" ht="18.75" customHeight="1">
       <c r="A134" s="3">
         <v>133</v>
       </c>
@@ -6864,7 +6912,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" ht="18.75" customHeight="1">
       <c r="A135" s="3">
         <v>134</v>
       </c>
@@ -6896,7 +6944,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" ht="18.75" customHeight="1">
       <c r="A136" s="3">
         <v>135</v>
       </c>
@@ -6928,7 +6976,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" ht="18.75" customHeight="1">
       <c r="A137" s="3">
         <v>136</v>
       </c>
@@ -6960,7 +7008,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" ht="18.75" customHeight="1">
       <c r="A138" s="3">
         <v>137</v>
       </c>
@@ -6992,7 +7040,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" ht="18.75" customHeight="1">
       <c r="A139" s="3">
         <v>138</v>
       </c>
@@ -7024,7 +7072,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" ht="18.75" customHeight="1">
       <c r="A140" s="3">
         <v>139</v>
       </c>
@@ -7056,7 +7104,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" ht="18.75" customHeight="1">
       <c r="A141" s="3">
         <v>140</v>
       </c>
@@ -7088,7 +7136,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" ht="18.75" customHeight="1">
       <c r="A142" s="3">
         <v>141</v>
       </c>
@@ -7120,7 +7168,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" ht="18.75" customHeight="1">
       <c r="A143" s="3">
         <v>142</v>
       </c>
@@ -7152,7 +7200,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" ht="18.75" customHeight="1">
       <c r="A144" s="3">
         <v>143</v>
       </c>
@@ -7184,7 +7232,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" ht="18.75" customHeight="1">
       <c r="A145" s="3">
         <v>144</v>
       </c>
@@ -7216,7 +7264,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" ht="18.75" customHeight="1">
       <c r="A146" s="3">
         <v>145</v>
       </c>
@@ -7248,7 +7296,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" ht="18.75" customHeight="1">
       <c r="A147" s="3">
         <v>146</v>
       </c>
@@ -7280,7 +7328,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" ht="18.75" customHeight="1">
       <c r="A148" s="3">
         <v>147</v>
       </c>
@@ -7312,7 +7360,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" ht="18.75" customHeight="1">
       <c r="A149" s="3">
         <v>148</v>
       </c>
@@ -7344,7 +7392,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" ht="18.75" customHeight="1">
       <c r="A150" s="3">
         <v>149</v>
       </c>
@@ -7376,7 +7424,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" ht="18.75" customHeight="1">
       <c r="A151" s="3">
         <v>150</v>
       </c>
@@ -7408,7 +7456,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" ht="18.75" customHeight="1">
       <c r="A152" s="3">
         <v>151</v>
       </c>
@@ -7440,7 +7488,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" ht="18.75" customHeight="1">
       <c r="A153" s="3">
         <v>152</v>
       </c>
@@ -7472,7 +7520,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" ht="18.75" customHeight="1">
       <c r="A154" s="3">
         <v>153</v>
       </c>
@@ -7504,7 +7552,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" ht="18.75" customHeight="1">
       <c r="A155" s="3">
         <v>154</v>
       </c>
@@ -7536,7 +7584,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" ht="18.75" customHeight="1">
       <c r="A156" s="3">
         <v>155</v>
       </c>
@@ -7568,7 +7616,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" ht="18.75" customHeight="1">
       <c r="A157" s="3">
         <v>156</v>
       </c>
@@ -7600,7 +7648,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" ht="18.75" customHeight="1">
       <c r="A158" s="3">
         <v>157</v>
       </c>
@@ -7632,7 +7680,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" ht="18.75" customHeight="1">
       <c r="A159" s="3">
         <v>158</v>
       </c>
@@ -7664,7 +7712,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" ht="18.75" customHeight="1">
       <c r="A160" s="3">
         <v>159</v>
       </c>
@@ -7696,7 +7744,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" ht="18.75" customHeight="1">
       <c r="A161" s="3">
         <v>160</v>
       </c>
@@ -7728,7 +7776,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" ht="18.75" customHeight="1">
       <c r="A162" s="3">
         <v>161</v>
       </c>
@@ -7760,7 +7808,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" ht="18.75" customHeight="1">
       <c r="A163" s="3">
         <v>162</v>
       </c>
@@ -7792,7 +7840,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" ht="18.75" customHeight="1">
       <c r="A164" s="3">
         <v>163</v>
       </c>
@@ -7824,7 +7872,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" ht="18.75" customHeight="1">
       <c r="A165" s="3">
         <v>164</v>
       </c>
@@ -7856,7 +7904,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" ht="18.75" customHeight="1">
       <c r="A166" s="3">
         <v>165</v>
       </c>
@@ -7888,7 +7936,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" ht="18.75" customHeight="1">
       <c r="A167" s="3">
         <v>166</v>
       </c>
@@ -7920,7 +7968,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" ht="18.75" customHeight="1">
       <c r="A168" s="3">
         <v>167</v>
       </c>
@@ -7952,7 +8000,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" ht="18.75" customHeight="1">
       <c r="A169" s="3">
         <v>168</v>
       </c>
@@ -7984,7 +8032,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" ht="18.75" customHeight="1">
       <c r="A170" s="3">
         <v>169</v>
       </c>
@@ -8016,7 +8064,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" ht="18.75" customHeight="1">
       <c r="A171" s="3">
         <v>170</v>
       </c>
@@ -8048,7 +8096,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" ht="18.75" customHeight="1">
       <c r="A172" s="3">
         <v>171</v>
       </c>
@@ -8080,7 +8128,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" ht="18.75" customHeight="1">
       <c r="A173" s="3">
         <v>172</v>
       </c>
@@ -8112,7 +8160,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" ht="18.75" customHeight="1">
       <c r="A174" s="3">
         <v>173</v>
       </c>
@@ -8144,7 +8192,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" ht="18.75" customHeight="1">
       <c r="A175" s="3">
         <v>174</v>
       </c>
@@ -8176,7 +8224,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" ht="18.75" customHeight="1">
       <c r="A176" s="3">
         <v>175</v>
       </c>
@@ -8208,7 +8256,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" ht="19.5" customHeight="1">
       <c r="A177" s="3">
         <v>176</v>
       </c>
@@ -8240,7 +8288,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" ht="20.25" customHeight="1">
       <c r="A178" s="3">
         <v>177</v>
       </c>
@@ -8272,7 +8320,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" ht="19.5" customHeight="1">
       <c r="A179" s="3">
         <v>178</v>
       </c>
@@ -8304,7 +8352,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" ht="20.25" customHeight="1">
       <c r="A180" s="3">
         <v>179</v>
       </c>
@@ -8336,7 +8384,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" ht="19.5" customHeight="1">
       <c r="A181" s="3">
         <v>180</v>
       </c>
@@ -8368,7 +8416,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" ht="20.25" customHeight="1">
       <c r="A182" s="3">
         <v>181</v>
       </c>
@@ -8400,7 +8448,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" ht="19.5" customHeight="1">
       <c r="A183" s="3">
         <v>182</v>
       </c>
@@ -8432,7 +8480,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" ht="20.25" customHeight="1">
       <c r="A184" s="3">
         <v>183</v>
       </c>
@@ -8464,7 +8512,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" ht="19.5" customHeight="1">
       <c r="A185" s="3">
         <v>184</v>
       </c>
@@ -8496,7 +8544,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" ht="20.25" customHeight="1">
       <c r="A186" s="3">
         <v>185</v>
       </c>
@@ -8528,7 +8576,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" ht="19.5" customHeight="1">
       <c r="A187" s="3">
         <v>186</v>
       </c>
@@ -8560,7 +8608,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" ht="20.25" customHeight="1">
       <c r="A188" s="3">
         <v>187</v>
       </c>
@@ -8592,7 +8640,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" ht="19.5" customHeight="1">
       <c r="A189" s="3">
         <v>188</v>
       </c>
@@ -8624,7 +8672,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" ht="20.25" customHeight="1">
       <c r="A190" s="3">
         <v>189</v>
       </c>
@@ -8656,7 +8704,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" ht="19.5" customHeight="1">
       <c r="A191" s="3">
         <v>190</v>
       </c>
@@ -8688,7 +8736,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" ht="20.25" customHeight="1">
       <c r="A192" s="3">
         <v>191</v>
       </c>
@@ -8720,7 +8768,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" ht="19.5" customHeight="1">
       <c r="A193" s="3">
         <v>192</v>
       </c>
@@ -8752,7 +8800,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" ht="20.25" customHeight="1">
       <c r="A194" s="3">
         <v>193</v>
       </c>
@@ -8784,7 +8832,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" ht="19.5" customHeight="1">
       <c r="A195" s="3">
         <v>194</v>
       </c>
@@ -8816,7 +8864,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" ht="20.25" customHeight="1">
       <c r="A196" s="3">
         <v>195</v>
       </c>
@@ -8848,7 +8896,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" ht="19.5" customHeight="1">
       <c r="A197" s="3">
         <v>196</v>
       </c>
@@ -8880,7 +8928,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" ht="20.25" customHeight="1">
       <c r="A198" s="3">
         <v>197</v>
       </c>
@@ -8912,7 +8960,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" ht="19.5" customHeight="1">
       <c r="A199" s="3">
         <v>198</v>
       </c>
@@ -8944,7 +8992,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" ht="20.25" customHeight="1">
       <c r="A200" s="3">
         <v>199</v>
       </c>
@@ -8976,7 +9024,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" ht="19.5" customHeight="1">
       <c r="A201" s="3">
         <v>200</v>
       </c>
@@ -9008,7 +9056,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" ht="18.75" customHeight="1">
       <c r="A202" s="3">
         <v>201</v>
       </c>
@@ -9040,7 +9088,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" ht="18.75" customHeight="1">
       <c r="A203" s="3">
         <v>202</v>
       </c>
@@ -9072,7 +9120,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" ht="18.75" customHeight="1">
       <c r="A204" s="3">
         <v>203</v>
       </c>
@@ -9104,7 +9152,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" ht="18.75" customHeight="1">
       <c r="A205" s="3">
         <v>204</v>
       </c>
@@ -9136,7 +9184,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" ht="18.75" customHeight="1">
       <c r="A206" s="3">
         <v>205</v>
       </c>
@@ -9168,7 +9216,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" ht="18.75" customHeight="1">
       <c r="A207" s="3">
         <v>206</v>
       </c>
@@ -9200,7 +9248,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" ht="18.75" customHeight="1">
       <c r="A208" s="3">
         <v>207</v>
       </c>
@@ -9232,7 +9280,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" ht="18.75" customHeight="1">
       <c r="A209" s="3">
         <v>208</v>
       </c>
@@ -9264,7 +9312,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" ht="18.75" customHeight="1">
       <c r="A210" s="3">
         <v>209</v>
       </c>
@@ -9296,7 +9344,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" ht="18.75" customHeight="1">
       <c r="A211" s="3">
         <v>210</v>
       </c>
@@ -9328,7 +9376,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" ht="18.75" customHeight="1">
       <c r="A212" s="3">
         <v>211</v>
       </c>
@@ -9360,7 +9408,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" ht="18.75" customHeight="1">
       <c r="A213" s="3">
         <v>212</v>
       </c>
@@ -9392,7 +9440,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" ht="18.75" customHeight="1">
       <c r="A214" s="3">
         <v>213</v>
       </c>
@@ -9424,7 +9472,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" ht="18.75" customHeight="1">
       <c r="A215" s="3">
         <v>214</v>
       </c>
@@ -9456,7 +9504,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" ht="18.75" customHeight="1">
       <c r="A216" s="3">
         <v>215</v>
       </c>
@@ -9488,7 +9536,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" ht="18.75" customHeight="1">
       <c r="A217" s="3">
         <v>216</v>
       </c>
@@ -9520,7 +9568,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" ht="18.75" customHeight="1">
       <c r="A218" s="3">
         <v>217</v>
       </c>
@@ -9552,7 +9600,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" ht="18.75" customHeight="1">
       <c r="A219" s="3">
         <v>218</v>
       </c>
@@ -9584,7 +9632,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" ht="18.75" customHeight="1">
       <c r="A220" s="3">
         <v>219</v>
       </c>
@@ -9616,7 +9664,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" ht="18.75" customHeight="1">
       <c r="A221" s="3">
         <v>220</v>
       </c>
@@ -9648,7 +9696,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" ht="18.75" customHeight="1">
       <c r="A222" s="3">
         <v>221</v>
       </c>
@@ -9680,7 +9728,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" ht="18.75" customHeight="1">
       <c r="A223" s="3">
         <v>222</v>
       </c>
@@ -9712,7 +9760,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" ht="18.75" customHeight="1">
       <c r="A224" s="3">
         <v>223</v>
       </c>
@@ -9744,7 +9792,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" ht="18.75" customHeight="1">
       <c r="A225" s="3">
         <v>224</v>
       </c>
@@ -9776,7 +9824,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" ht="18.75" customHeight="1">
       <c r="A226" s="3">
         <v>225</v>
       </c>
@@ -9808,7 +9856,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" ht="18.75" customHeight="1">
       <c r="A227" s="3">
         <v>226</v>
       </c>
@@ -9840,7 +9888,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" ht="18.75" customHeight="1">
       <c r="A228" s="3">
         <v>227</v>
       </c>
@@ -9872,7 +9920,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" ht="18.75" customHeight="1">
       <c r="A229" s="3">
         <v>228</v>
       </c>
@@ -9904,7 +9952,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" ht="18.75" customHeight="1">
       <c r="A230" s="3">
         <v>229</v>
       </c>
@@ -9936,7 +9984,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" ht="18.75" customHeight="1">
       <c r="A231" s="3">
         <v>230</v>
       </c>
@@ -9968,7 +10016,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" ht="18.75" customHeight="1">
       <c r="A232" s="3">
         <v>231</v>
       </c>
@@ -10000,7 +10048,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" ht="18.75" customHeight="1">
       <c r="A233" s="3">
         <v>232</v>
       </c>
@@ -10032,7 +10080,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" ht="18.75" customHeight="1">
       <c r="A234" s="3">
         <v>233</v>
       </c>
@@ -10064,7 +10112,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" ht="18.75" customHeight="1">
       <c r="A235" s="3">
         <v>234</v>
       </c>
@@ -10096,7 +10144,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" ht="18.75" customHeight="1">
       <c r="A236" s="3">
         <v>235</v>
       </c>
@@ -10128,7 +10176,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" ht="18.75" customHeight="1">
       <c r="A237" s="3">
         <v>236</v>
       </c>
@@ -10160,7 +10208,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" ht="18.75" customHeight="1">
       <c r="A238" s="3">
         <v>237</v>
       </c>
@@ -10192,7 +10240,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" ht="18.75" customHeight="1">
       <c r="A239" s="3">
         <v>238</v>
       </c>
@@ -10224,7 +10272,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" ht="18.75" customHeight="1">
       <c r="A240" s="3">
         <v>239</v>
       </c>
@@ -10256,7 +10304,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:11" ht="18.75" customHeight="1">
       <c r="A241" s="3">
         <v>240</v>
       </c>
@@ -10288,7 +10336,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:11" ht="18.75" customHeight="1">
       <c r="A242" s="3">
         <v>241</v>
       </c>
@@ -10320,7 +10368,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:11" ht="18.75" customHeight="1">
       <c r="A243" s="3">
         <v>242</v>
       </c>
@@ -10352,7 +10400,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:11" ht="18.75" customHeight="1">
       <c r="A244" s="3">
         <v>243</v>
       </c>
@@ -10384,7 +10432,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:11" ht="18.75" customHeight="1">
       <c r="A245" s="3">
         <v>244</v>
       </c>
@@ -10416,7 +10464,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:11" ht="18.75" customHeight="1">
       <c r="A246" s="3">
         <v>245</v>
       </c>
@@ -10448,7 +10496,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="247" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:11" ht="18.75" customHeight="1">
       <c r="A247" s="3">
         <v>246</v>
       </c>
@@ -10480,7 +10528,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:11" ht="18.75" customHeight="1">
       <c r="A248" s="4">
         <v>247</v>
       </c>
@@ -10515,7 +10563,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="249" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:11" ht="18.75" customHeight="1">
       <c r="A249" s="4">
         <v>248</v>
       </c>
@@ -10550,7 +10598,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="250" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:11" ht="18.75" customHeight="1">
       <c r="A250" s="4">
         <v>249</v>
       </c>
@@ -10585,7 +10633,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:11" ht="18.75" customHeight="1">
       <c r="A251" s="4">
         <v>250</v>
       </c>
@@ -10620,7 +10668,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:11" ht="18.75" customHeight="1">
       <c r="A252" s="4">
         <v>251</v>
       </c>
@@ -10655,7 +10703,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="253" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:11" ht="18.75" customHeight="1">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -10690,7 +10738,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="254" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:11" ht="18.75" customHeight="1">
       <c r="A254" s="4">
         <v>253</v>
       </c>
@@ -10725,7 +10773,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="255" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:11" ht="18.75" customHeight="1">
       <c r="A255" s="4">
         <v>254</v>
       </c>
@@ -10760,7 +10808,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="256" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:11" ht="18.75" customHeight="1">
       <c r="A256" s="4">
         <v>255</v>
       </c>
@@ -10795,7 +10843,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="257" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:11" ht="18.75" customHeight="1">
       <c r="A257" s="4">
         <v>256</v>
       </c>
@@ -10830,7 +10878,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="258" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:11" ht="18.75" customHeight="1">
       <c r="A258" s="4">
         <v>257</v>
       </c>
@@ -10865,7 +10913,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="259" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:11" ht="18.75" customHeight="1">
       <c r="A259" s="4">
         <v>258</v>
       </c>
@@ -10900,7 +10948,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="260" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:11" ht="18.75" customHeight="1">
       <c r="A260" s="4">
         <v>259</v>
       </c>
@@ -10935,7 +10983,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="261" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:11" ht="18.75" customHeight="1">
       <c r="A261" s="4">
         <v>260</v>
       </c>
@@ -10970,7 +11018,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="262" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:11" ht="18.75" customHeight="1">
       <c r="A262" s="4">
         <v>261</v>
       </c>
@@ -11005,7 +11053,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="263" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:11" ht="18.75" customHeight="1">
       <c r="A263" s="4">
         <v>262</v>
       </c>
@@ -11040,7 +11088,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="264" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:11" ht="18.75" customHeight="1">
       <c r="A264" s="4">
         <v>263</v>
       </c>
@@ -11075,7 +11123,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:11" ht="18.75" customHeight="1">
       <c r="A265" s="4">
         <v>264</v>
       </c>
@@ -11110,7 +11158,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:11" ht="18.75" customHeight="1">
       <c r="A266" s="4">
         <v>265</v>
       </c>
@@ -11145,7 +11193,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="267" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:11" ht="18.75" customHeight="1">
       <c r="A267" s="4">
         <v>266</v>
       </c>
@@ -11180,7 +11228,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="268" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:11" ht="18.75" customHeight="1">
       <c r="A268" s="4">
         <v>267</v>
       </c>
@@ -11215,7 +11263,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:11" ht="18.75" customHeight="1">
       <c r="A269" s="4">
         <v>268</v>
       </c>
@@ -11250,7 +11298,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="270" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:11" ht="18.75" customHeight="1">
       <c r="A270" s="4">
         <v>269</v>
       </c>
@@ -11285,7 +11333,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:11" ht="18.75" customHeight="1">
       <c r="A271" s="4">
         <v>270</v>
       </c>
@@ -11320,7 +11368,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:11" ht="18.75" customHeight="1">
       <c r="A272" s="4">
         <v>271</v>
       </c>
@@ -11355,7 +11403,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="273" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:11" ht="18.75" customHeight="1">
       <c r="A273" s="4">
         <v>272</v>
       </c>
@@ -11390,7 +11438,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="274" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:11" ht="18.75" customHeight="1">
       <c r="A274" s="4">
         <v>273</v>
       </c>
@@ -11425,7 +11473,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="275" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:11" ht="18.75" customHeight="1">
       <c r="A275" s="4">
         <v>274</v>
       </c>
@@ -11460,7 +11508,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="276" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:11" ht="18.75" customHeight="1">
       <c r="A276" s="4">
         <v>275</v>
       </c>
@@ -11495,7 +11543,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="277" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:11" ht="18.75" customHeight="1">
       <c r="A277" s="4">
         <v>276</v>
       </c>
@@ -11530,7 +11578,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:11" ht="18.75" customHeight="1">
       <c r="A278" s="4">
         <v>277</v>
       </c>
@@ -11565,7 +11613,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:11" ht="18.75" customHeight="1">
       <c r="A279" s="4">
         <v>278</v>
       </c>
@@ -11600,7 +11648,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:11" ht="18.75" customHeight="1">
       <c r="A280" s="4">
         <v>279</v>
       </c>
@@ -11635,7 +11683,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:11" ht="18.75" customHeight="1">
       <c r="A281" s="4">
         <v>280</v>
       </c>
@@ -11670,7 +11718,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:11" ht="18.75" customHeight="1">
       <c r="A282" s="4">
         <v>281</v>
       </c>
@@ -11705,7 +11753,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:11" ht="18.75" customHeight="1">
       <c r="A283" s="4">
         <v>282</v>
       </c>
@@ -11740,7 +11788,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:11" ht="18.75" customHeight="1">
       <c r="A284" s="4">
         <v>283</v>
       </c>
@@ -11775,7 +11823,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:11" ht="18.75" customHeight="1">
       <c r="A285" s="4">
         <v>284</v>
       </c>
@@ -11810,7 +11858,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:11" ht="18.75" customHeight="1">
       <c r="A286" s="4">
         <v>285</v>
       </c>
@@ -11845,7 +11893,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:11" ht="18.75" customHeight="1">
       <c r="A287" s="4">
         <v>286</v>
       </c>
@@ -11880,7 +11928,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:11" ht="18.75" customHeight="1">
       <c r="A288" s="4">
         <v>287</v>
       </c>
@@ -11915,7 +11963,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="289" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:11" ht="18.75" customHeight="1">
       <c r="A289" s="4">
         <v>288</v>
       </c>
@@ -11950,7 +11998,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:11" ht="18.75" customHeight="1">
       <c r="A290" s="4">
         <v>289</v>
       </c>
@@ -11985,7 +12033,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:11" ht="18.75" customHeight="1">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -12020,7 +12068,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="292" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:11" ht="18.75" customHeight="1">
       <c r="A292" s="4">
         <v>291</v>
       </c>
@@ -12055,7 +12103,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="293" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:11" ht="18.75" customHeight="1">
       <c r="A293" s="4">
         <v>292</v>
       </c>
@@ -12090,7 +12138,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="294" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:11" ht="18.75" customHeight="1">
       <c r="A294" s="4">
         <v>293</v>
       </c>
@@ -12125,7 +12173,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:11" ht="18.75" customHeight="1">
       <c r="A295" s="4">
         <v>294</v>
       </c>
@@ -12160,7 +12208,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:11" ht="18.75" customHeight="1">
       <c r="A296" s="4">
         <v>295</v>
       </c>
@@ -12195,7 +12243,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:11" ht="18.75" customHeight="1">
       <c r="A297" s="4">
         <v>296</v>
       </c>
@@ -12230,7 +12278,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:11" ht="18.75" customHeight="1">
       <c r="A298" s="4">
         <v>297</v>
       </c>
@@ -12265,7 +12313,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:11" ht="18.75" customHeight="1">
       <c r="A299" s="4">
         <v>298</v>
       </c>
@@ -12300,7 +12348,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:11" ht="18.75" customHeight="1">
       <c r="A300" s="4">
         <v>299</v>
       </c>
@@ -12335,7 +12383,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:11" ht="18.75" customHeight="1">
       <c r="A301" s="4">
         <v>300</v>
       </c>
@@ -12370,7 +12418,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:11" ht="18.75" customHeight="1">
       <c r="A302" s="4">
         <v>301</v>
       </c>
@@ -12405,7 +12453,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:11" ht="18.75" customHeight="1">
       <c r="A303" s="4">
         <v>302</v>
       </c>
@@ -12440,7 +12488,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:11" ht="18.75" customHeight="1">
       <c r="A304" s="4">
         <v>303</v>
       </c>
@@ -12475,7 +12523,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:11" ht="18.75" customHeight="1">
       <c r="A305" s="4">
         <v>304</v>
       </c>
@@ -12510,7 +12558,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="306" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:11" ht="18.75" customHeight="1">
       <c r="A306" s="4">
         <v>305</v>
       </c>
@@ -12545,7 +12593,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:11" ht="18.75" customHeight="1">
       <c r="A307" s="4">
         <v>306</v>
       </c>
@@ -12580,7 +12628,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:11" ht="18.75" customHeight="1">
       <c r="A308" s="4">
         <v>307</v>
       </c>
@@ -12615,7 +12663,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:11" ht="18.75" customHeight="1">
       <c r="A309" s="4">
         <v>308</v>
       </c>
@@ -12650,7 +12698,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:11" ht="15">
       <c r="A310" s="4">
         <v>309</v>
       </c>
@@ -12682,7 +12730,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:11" ht="15">
       <c r="A311" s="4">
         <v>310</v>
       </c>
@@ -12714,7 +12762,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:11" ht="15">
       <c r="A312" s="4">
         <v>311</v>
       </c>
@@ -12746,7 +12794,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:11" ht="15">
       <c r="A313" s="4">
         <v>312</v>
       </c>
@@ -12778,7 +12826,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:11" ht="15">
       <c r="A314" s="4">
         <v>313</v>
       </c>
@@ -12810,7 +12858,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:11" ht="15">
       <c r="A315" s="4">
         <v>314</v>
       </c>
@@ -12842,7 +12890,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:11" ht="15">
       <c r="A316" s="4">
         <v>315</v>
       </c>
@@ -12874,7 +12922,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:11" ht="15">
       <c r="A317" s="4">
         <v>316</v>
       </c>
@@ -12906,7 +12954,7 @@
         <v>315.228571428571</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:11" ht="15">
       <c r="A318" s="4">
         <v>317</v>
       </c>
@@ -12938,7 +12986,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:11" ht="15">
       <c r="A319" s="4">
         <v>318</v>
       </c>
@@ -12970,7 +13018,7 @@
         <v>316.88571428571402</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:11" ht="15">
       <c r="A320" s="4">
         <v>319</v>
       </c>
@@ -13002,7 +13050,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:10" ht="15">
       <c r="A321" s="4">
         <v>320</v>
       </c>
@@ -13034,7 +13082,7 @@
         <v>318.54285714285697</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:10" ht="15">
       <c r="A322" s="4">
         <v>321</v>
       </c>
@@ -13066,7 +13114,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:10" ht="15">
       <c r="A323" s="4">
         <v>322</v>
       </c>
@@ -13096,6 +13144,70 @@
       </c>
       <c r="J323" s="4">
         <v>321</v>
+      </c>
+    </row>
+    <row r="324" spans="1:10" ht="15">
+      <c r="A324" s="4">
+        <v>323</v>
+      </c>
+      <c r="B324" t="s">
+        <v>700</v>
+      </c>
+      <c r="C324" t="s">
+        <v>701</v>
+      </c>
+      <c r="D324" t="s">
+        <v>703</v>
+      </c>
+      <c r="E324" t="s">
+        <v>702</v>
+      </c>
+      <c r="F324" t="s">
+        <v>704</v>
+      </c>
+      <c r="G324" t="s">
+        <v>705</v>
+      </c>
+      <c r="H324" t="s">
+        <v>706</v>
+      </c>
+      <c r="I324" t="s">
+        <v>711</v>
+      </c>
+      <c r="J324" s="4">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="325" spans="1:10" ht="15">
+      <c r="A325" s="4">
+        <v>324</v>
+      </c>
+      <c r="B325" t="s">
+        <v>707</v>
+      </c>
+      <c r="C325" t="s">
+        <v>708</v>
+      </c>
+      <c r="D325" t="s">
+        <v>709</v>
+      </c>
+      <c r="E325" t="s">
+        <v>710</v>
+      </c>
+      <c r="F325" t="s">
+        <v>704</v>
+      </c>
+      <c r="G325" t="s">
+        <v>705</v>
+      </c>
+      <c r="H325" t="s">
+        <v>706</v>
+      </c>
+      <c r="I325" t="s">
+        <v>711</v>
+      </c>
+      <c r="J325" s="4">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
